--- a/pricing/labor-units-starter.xlsx
+++ b/pricing/labor-units-starter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="581">
   <si>
     <t>ID</t>
   </si>
@@ -678,33 +678,1047 @@
     <t>Assembly ID</t>
   </si>
   <si>
+    <t>Plan #</t>
+  </si>
+  <si>
     <t>Assembly</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>DV1</t>
+  </si>
+  <si>
     <t>Duplex receptacle standard</t>
   </si>
   <si>
+    <t>Devices</t>
+  </si>
+  <si>
+    <t>DV4</t>
+  </si>
+  <si>
     <t>Single-pole switch</t>
   </si>
   <si>
+    <t>DV2</t>
+  </si>
+  <si>
     <t>GFCI receptacle</t>
   </si>
   <si>
+    <t>LT1</t>
+  </si>
+  <si>
+    <t>Surface-mount ceiling fixture</t>
+  </si>
+  <si>
+    <t>Lighting</t>
+  </si>
+  <si>
+    <t>LT4</t>
+  </si>
+  <si>
+    <t>Recessed can new construction, 6"</t>
+  </si>
+  <si>
+    <t>not seeded yet: hours not set needs Track A's 0123 (the column cannot hold NULL yet)</t>
+  </si>
+  <si>
+    <t>LT7</t>
+  </si>
+  <si>
+    <t>Wafer LED downlight, 6" (canless)</t>
+  </si>
+  <si>
+    <t>DV3</t>
+  </si>
+  <si>
     <t>Dedicated 20A receptacle</t>
   </si>
   <si>
-    <t>Surface-mount ceiling fixture</t>
+    <t>DV13</t>
+  </si>
+  <si>
+    <t>3-way switch</t>
+  </si>
+  <si>
+    <t>DV5</t>
   </si>
   <si>
     <t>Dimmer switch</t>
   </si>
   <si>
+    <t>DV20</t>
+  </si>
+  <si>
+    <t>Duplex receptacle, MC</t>
+  </si>
+  <si>
+    <t>DV26</t>
+  </si>
+  <si>
+    <t>Single-pole switch, MC</t>
+  </si>
+  <si>
+    <t>LT19</t>
+  </si>
+  <si>
+    <t>2x4 LED troffer, lay-in</t>
+  </si>
+  <si>
+    <t>DV7</t>
+  </si>
+  <si>
+    <t>20A duplex receptacle</t>
+  </si>
+  <si>
+    <t>DV9</t>
+  </si>
+  <si>
+    <t>AFCI receptacle</t>
+  </si>
+  <si>
+    <t>LT2</t>
+  </si>
+  <si>
     <t>Ceiling fan standard</t>
   </si>
   <si>
+    <t>MS1</t>
+  </si>
+  <si>
+    <t>Junction box, 4" square</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>not seeded yet: its category waits on Track A's 0122; hours not set needs Track A's 0123 (the column cannot hold NULL yet)</t>
+  </si>
+  <si>
+    <t>DV21</t>
+  </si>
+  <si>
+    <t>GFCI receptacle, MC</t>
+  </si>
+  <si>
+    <t>DV16</t>
+  </si>
+  <si>
+    <t>Two switches, one box</t>
+  </si>
+  <si>
+    <t>DV8</t>
+  </si>
+  <si>
+    <t>Outdoor GFCI receptacle, in-use cover</t>
+  </si>
+  <si>
+    <t>LT27</t>
+  </si>
+  <si>
+    <t>LT28</t>
+  </si>
+  <si>
+    <t>Emergency light / exit combo</t>
+  </si>
+  <si>
+    <t>LT22</t>
+  </si>
+  <si>
+    <t>4 ft LED strip, surface / suspended</t>
+  </si>
+  <si>
+    <t>LT20</t>
+  </si>
+  <si>
+    <t>2x2 LED troffer, lay-in</t>
+  </si>
+  <si>
+    <t>DV6</t>
+  </si>
+  <si>
+    <t>Duplex receptacle retrofit</t>
+  </si>
+  <si>
+    <t>LT6</t>
+  </si>
+  <si>
+    <t>Recessed can retrofit, 6"</t>
+  </si>
+  <si>
+    <t>LT8</t>
+  </si>
+  <si>
+    <t>Wafer LED downlight, 4" (canless)</t>
+  </si>
+  <si>
+    <t>LT5</t>
+  </si>
+  <si>
+    <t>Recessed can new construction, 4"</t>
+  </si>
+  <si>
+    <t>PG7</t>
+  </si>
+  <si>
+    <t>Breaker add, single-pole</t>
+  </si>
+  <si>
+    <t>PG8</t>
+  </si>
+  <si>
+    <t>Breaker add, 2-pole</t>
+  </si>
+  <si>
+    <t>RS7</t>
+  </si>
+  <si>
+    <t>Bath exhaust fan wiring</t>
+  </si>
+  <si>
+    <t>Equipment Connections</t>
+  </si>
+  <si>
+    <t>RS9</t>
+  </si>
+  <si>
+    <t>Combination smoke/CO detector</t>
+  </si>
+  <si>
+    <t>DV22</t>
+  </si>
+  <si>
+    <t>Quad receptacle, MC</t>
+  </si>
+  <si>
+    <t>DV11</t>
+  </si>
+  <si>
+    <t>Quad receptacle</t>
+  </si>
+  <si>
+    <t>DV27</t>
+  </si>
+  <si>
+    <t>3-way switch, MC</t>
+  </si>
+  <si>
+    <t>DV29</t>
+  </si>
+  <si>
+    <t>Wall occupancy sensor, MC</t>
+  </si>
+  <si>
+    <t>DV30</t>
+  </si>
+  <si>
+    <t>Ceiling occupancy sensor + power pack</t>
+  </si>
+  <si>
+    <t>MS6</t>
+  </si>
+  <si>
+    <t>Data drop, Cat6 (commercial)</t>
+  </si>
+  <si>
+    <t>Low Voltage/EMS</t>
+  </si>
+  <si>
+    <t>MS7</t>
+  </si>
+  <si>
+    <t>Data drop, Cat6 (resi)</t>
+  </si>
+  <si>
+    <t>MS2</t>
+  </si>
+  <si>
+    <t>Junction box above lay-in ceiling</t>
+  </si>
+  <si>
+    <t>LT12</t>
+  </si>
+  <si>
+    <t>Vanity light</t>
+  </si>
+  <si>
+    <t>LT13</t>
+  </si>
+  <si>
+    <t>Wall sconce</t>
+  </si>
+  <si>
+    <t>LT10</t>
+  </si>
+  <si>
+    <t>Pendant light</t>
+  </si>
+  <si>
+    <t>LT15</t>
+  </si>
+  <si>
+    <t>Exterior porch light</t>
+  </si>
+  <si>
+    <t>LT14</t>
+  </si>
+  <si>
+    <t>Under-cabinet light</t>
+  </si>
+  <si>
+    <t>DV10</t>
+  </si>
+  <si>
+    <t>USB combo receptacle</t>
+  </si>
+  <si>
+    <t>DV12</t>
+  </si>
+  <si>
+    <t>Switch/receptacle combo</t>
+  </si>
+  <si>
+    <t>DV14</t>
+  </si>
+  <si>
+    <t>4-way switch</t>
+  </si>
+  <si>
+    <t>DV15</t>
+  </si>
+  <si>
+    <t>3-way dimmer</t>
+  </si>
+  <si>
+    <t>DV17</t>
+  </si>
+  <si>
+    <t>Three switches, one box</t>
+  </si>
+  <si>
+    <t>DV18</t>
+  </si>
+  <si>
+    <t>Fan/light combo control</t>
+  </si>
+  <si>
+    <t>DV19</t>
+  </si>
+  <si>
+    <t>Timer / smart / vacancy switch</t>
+  </si>
+  <si>
+    <t>DV23</t>
+  </si>
+  <si>
+    <t>Dedicated 20A receptacle, MC</t>
+  </si>
+  <si>
+    <t>RS4</t>
+  </si>
+  <si>
+    <t>Dishwasher connection</t>
+  </si>
+  <si>
+    <t>RS5</t>
+  </si>
+  <si>
+    <t>Garbage disposal, switched</t>
+  </si>
+  <si>
+    <t>RS6</t>
+  </si>
+  <si>
+    <t>Range hood / microwave circuit</t>
+  </si>
+  <si>
+    <t>RS1</t>
+  </si>
+  <si>
+    <t>Range receptacle, 50A</t>
+  </si>
+  <si>
+    <t>RS2</t>
+  </si>
+  <si>
+    <t>Dryer receptacle, 30A</t>
+  </si>
+  <si>
+    <t>RS3</t>
+  </si>
+  <si>
+    <t>Electric water heater connection</t>
+  </si>
+  <si>
+    <t>MH1</t>
+  </si>
+  <si>
+    <t>HVAC condenser disconnect + whip</t>
+  </si>
+  <si>
+    <t>MH2</t>
+  </si>
+  <si>
+    <t>Furnace / air handler, 120V</t>
+  </si>
+  <si>
+    <t>PG1</t>
+  </si>
+  <si>
     <t>200A main panel furnish and install</t>
   </si>
   <si>
+    <t>PG9</t>
+  </si>
+  <si>
+    <t>Breaker swap to AFCI/GFCI</t>
+  </si>
+  <si>
+    <t>DR16</t>
+  </si>
+  <si>
+    <t>Replace receptacle like-for-like</t>
+  </si>
+  <si>
+    <t>Demo &amp; Retrofit</t>
+  </si>
+  <si>
+    <t>DR17</t>
+  </si>
+  <si>
+    <t>Replace receptacle with GFCI</t>
+  </si>
+  <si>
+    <t>DR18</t>
+  </si>
+  <si>
+    <t>Replace switch with occupancy sensor</t>
+  </si>
+  <si>
+    <t>DR2</t>
+  </si>
+  <si>
+    <t>Demo device, blank plate</t>
+  </si>
+  <si>
+    <t>DR1</t>
+  </si>
+  <si>
+    <t>Demo fixture, blank the box</t>
+  </si>
+  <si>
+    <t>DR7</t>
+  </si>
+  <si>
+    <t>Troffer LED retrofit kit</t>
+  </si>
+  <si>
+    <t>DR8</t>
+  </si>
+  <si>
+    <t>4 ft fluorescent to LED, ballast bypass (2-lamp)</t>
+  </si>
+  <si>
+    <t>DR6</t>
+  </si>
+  <si>
+    <t>Replace troffer like-for-like</t>
+  </si>
+  <si>
+    <t>DR3</t>
+  </si>
+  <si>
+    <t>Demo lay-in fixture, make safe above ceiling</t>
+  </si>
+  <si>
+    <t>DR4</t>
+  </si>
+  <si>
+    <t>Demo circuit back to panel</t>
+  </si>
+  <si>
+    <t>DR5</t>
+  </si>
+  <si>
+    <t>Relocate lay-in troffer (≤6 ft)</t>
+  </si>
+  <si>
+    <t>DR19</t>
+  </si>
+  <si>
+    <t>Relocate receptacle (wall move), MC</t>
+  </si>
+  <si>
+    <t>DR20</t>
+  </si>
+  <si>
+    <t>Recessed can LED retrofit (resi)</t>
+  </si>
+  <si>
+    <t>LT21</t>
+  </si>
+  <si>
+    <t>1x4 LED troffer, lay-in</t>
+  </si>
+  <si>
+    <t>LT23</t>
+  </si>
+  <si>
+    <t>8 ft LED strip (sales floor rows)</t>
+  </si>
+  <si>
+    <t>LT24</t>
+  </si>
+  <si>
+    <t>4 ft LED wraparound (back room)</t>
+  </si>
+  <si>
+    <t>LT25</t>
+  </si>
+  <si>
+    <t>4 ft vapor tight (cooler, dock)</t>
+  </si>
+  <si>
+    <t>LT26</t>
+  </si>
+  <si>
+    <t>High bay</t>
+  </si>
+  <si>
+    <t>LT29</t>
+  </si>
+  <si>
+    <t>Exterior wall pack</t>
+  </si>
+  <si>
+    <t>LT16</t>
+  </si>
+  <si>
+    <t>Flood / security light</t>
+  </si>
+  <si>
+    <t>LT9</t>
+  </si>
+  <si>
+    <t>Shower light, wet-rated</t>
+  </si>
+  <si>
+    <t>LT3</t>
+  </si>
+  <si>
+    <t>Ceiling fan, retrofit brace</t>
+  </si>
+  <si>
+    <t>LT11</t>
+  </si>
+  <si>
+    <t>Chandelier, heavy bracing</t>
+  </si>
+  <si>
+    <t>RS8</t>
+  </si>
+  <si>
+    <t>Bath fan/light combo, humidity switch</t>
+  </si>
+  <si>
+    <t>RS17</t>
+  </si>
+  <si>
+    <t>Sump pump circuit</t>
+  </si>
+  <si>
+    <t>RS12</t>
+  </si>
+  <si>
+    <t>EV charger circuit, 48A hardwired</t>
+  </si>
+  <si>
+    <t>RS13</t>
+  </si>
+  <si>
+    <t>EV / RV receptacle, 50A (NEMA 14-50)</t>
+  </si>
+  <si>
+    <t>RS10</t>
+  </si>
+  <si>
+    <t>Doorbell, wired</t>
+  </si>
+  <si>
+    <t>RS11</t>
+  </si>
+  <si>
+    <t>Video doorbell wiring</t>
+  </si>
+  <si>
+    <t>RS20</t>
+  </si>
+  <si>
+    <t>Attic fan with thermostat</t>
+  </si>
+  <si>
+    <t>RS19</t>
+  </si>
+  <si>
+    <t>Baseboard heater, 240V</t>
+  </si>
+  <si>
+    <t>MS4</t>
+  </si>
+  <si>
+    <t>Firestop penetration</t>
+  </si>
+  <si>
+    <t>MS13</t>
+  </si>
+  <si>
+    <t>Panel labelling (existing panel)</t>
+  </si>
+  <si>
+    <t>MS8</t>
+  </si>
+  <si>
+    <t>Cable TV drop</t>
+  </si>
+  <si>
+    <t>MS9</t>
+  </si>
+  <si>
+    <t>Security camera drop</t>
+  </si>
+  <si>
+    <t>MS10</t>
+  </si>
+  <si>
+    <t>In-ceiling speaker</t>
+  </si>
+  <si>
+    <t>MS12</t>
+  </si>
+  <si>
+    <t>Structured media enclosure (resi)</t>
+  </si>
+  <si>
+    <t>MS5</t>
+  </si>
+  <si>
+    <t>Conduit trapeze (strut rack), per hanger</t>
+  </si>
+  <si>
+    <t>MS3</t>
+  </si>
+  <si>
+    <t>Pull box, 12x12</t>
+  </si>
+  <si>
+    <t>MS14</t>
+  </si>
+  <si>
+    <t>Temporary lighting string, per 100 ft</t>
+  </si>
+  <si>
+    <t>MS11</t>
+  </si>
+  <si>
+    <t>Network patch panel, 24-port</t>
+  </si>
+  <si>
+    <t>DV24</t>
+  </si>
+  <si>
+    <t>Isolated-ground receptacle (cash wrap)</t>
+  </si>
+  <si>
+    <t>DV25</t>
+  </si>
+  <si>
+    <t>Controlled receptacle (plug load)</t>
+  </si>
+  <si>
+    <t>DV28</t>
+  </si>
+  <si>
+    <t>Key switch, MC</t>
+  </si>
+  <si>
+    <t>DV31</t>
+  </si>
+  <si>
+    <t>0-10V dimmer, MC</t>
+  </si>
+  <si>
+    <t>DV32</t>
+  </si>
+  <si>
+    <t>Floor receptacle, poke-through</t>
+  </si>
+  <si>
+    <t>DV33</t>
+  </si>
+  <si>
+    <t>Floor box receptacle (slab)</t>
+  </si>
+  <si>
+    <t>DV34</t>
+  </si>
+  <si>
+    <t>Surface raceway receptacle (block wall)</t>
+  </si>
+  <si>
+    <t>not seeded yet: a part is not in the catalog; hours not set needs Track A's 0123 (the column cannot hold NULL yet) (Surface raceway, 10 ft, Surface raceway device box, Surface raceway cover plate, Surface raceway entrance fitting)</t>
+  </si>
+  <si>
+    <t>CS3</t>
+  </si>
+  <si>
+    <t>Hand dryer</t>
+  </si>
+  <si>
+    <t>CS4</t>
+  </si>
+  <si>
+    <t>Drinking fountain / EWC</t>
+  </si>
+  <si>
+    <t>CS5</t>
+  </si>
+  <si>
+    <t>Reach-in cooler / freezer receptacle</t>
+  </si>
+  <si>
+    <t>CS6</t>
+  </si>
+  <si>
+    <t>Twist-lock receptacle, L5-20</t>
+  </si>
+  <si>
+    <t>CS7</t>
+  </si>
+  <si>
+    <t>Twist-lock receptacle, L6-30</t>
+  </si>
+  <si>
+    <t>CS8</t>
+  </si>
+  <si>
+    <t>Twist-lock receptacle, L14-30</t>
+  </si>
+  <si>
+    <t>CS1</t>
+  </si>
+  <si>
+    <t>Sign circuit and disconnect</t>
+  </si>
+  <si>
+    <t>CS2</t>
+  </si>
+  <si>
+    <t>Time clock and lighting contactor</t>
+  </si>
+  <si>
+    <t>CS11</t>
+  </si>
+  <si>
+    <t>Fire alarm pull station</t>
+  </si>
+  <si>
+    <t>CS12</t>
+  </si>
+  <si>
+    <t>Fire alarm horn/strobe</t>
+  </si>
+  <si>
+    <t>CS13</t>
+  </si>
+  <si>
+    <t>Fire alarm smoke detector (system)</t>
+  </si>
+  <si>
+    <t>CS14</t>
+  </si>
+  <si>
+    <t>Duct smoke detector</t>
+  </si>
+  <si>
+    <t>CS9</t>
+  </si>
+  <si>
+    <t>Tele-power pole</t>
+  </si>
+  <si>
+    <t>CS10</t>
+  </si>
+  <si>
+    <t>Modular furniture feed</t>
+  </si>
+  <si>
+    <t>CS15</t>
+  </si>
+  <si>
+    <t>Kitchen hood shunt interface</t>
+  </si>
+  <si>
+    <t>CS16</t>
+  </si>
+  <si>
+    <t>Knox box</t>
+  </si>
+  <si>
+    <t>PG10</t>
+  </si>
+  <si>
+    <t>Whole-house surge protector</t>
+  </si>
+  <si>
+    <t>PG11</t>
+  </si>
+  <si>
+    <t>Grounding electrode system</t>
+  </si>
+  <si>
+    <t>PG5</t>
+  </si>
+  <si>
+    <t>Subpanel, 100A (resi, 60A feed)</t>
+  </si>
+  <si>
+    <t>PG4</t>
+  </si>
+  <si>
+    <t>Panel replacement like-for-like, 200A</t>
+  </si>
+  <si>
+    <t>PG2</t>
+  </si>
+  <si>
+    <t>Service upgrade 200A, overhead</t>
+  </si>
+  <si>
+    <t>PG3</t>
+  </si>
+  <si>
+    <t>Service upgrade 200A, meter-main outdoor</t>
+  </si>
+  <si>
+    <t>PG6</t>
+  </si>
+  <si>
+    <t>Load center relocate</t>
+  </si>
+  <si>
+    <t>PG12</t>
+  </si>
+  <si>
+    <t>Panelboard 225A 3-phase, main-lug</t>
+  </si>
+  <si>
+    <t>PG13</t>
+  </si>
+  <si>
+    <t>Panelboard 225A 3-phase, main breaker</t>
+  </si>
+  <si>
+    <t>PG14</t>
+  </si>
+  <si>
+    <t>Panelboard 400A 3-phase, main breaker</t>
+  </si>
+  <si>
+    <t>PG15</t>
+  </si>
+  <si>
+    <t>Feeder breaker, 3-pole</t>
+  </si>
+  <si>
+    <t>PG17</t>
+  </si>
+  <si>
+    <t>Safety switch, 100A fused</t>
+  </si>
+  <si>
+    <t>PG18</t>
+  </si>
+  <si>
+    <t>Building surge protective device</t>
+  </si>
+  <si>
+    <t>PG16</t>
+  </si>
+  <si>
+    <t>Dry-type transformer, 45 kVA</t>
+  </si>
+  <si>
+    <t>PG19</t>
+  </si>
+  <si>
+    <t>Standby generator hookup</t>
+  </si>
+  <si>
+    <t>PG20</t>
+  </si>
+  <si>
+    <t>Temporary power pole</t>
+  </si>
+  <si>
+    <t>RS18</t>
+  </si>
+  <si>
+    <t>Generator inlet and interlock</t>
+  </si>
+  <si>
+    <t>RS14</t>
+  </si>
+  <si>
+    <t>Hot tub / spa connection</t>
+  </si>
+  <si>
+    <t>RS15</t>
+  </si>
+  <si>
+    <t>Pool pump connection</t>
+  </si>
+  <si>
+    <t>RS16</t>
+  </si>
+  <si>
+    <t>Well pump connection</t>
+  </si>
+  <si>
+    <t>MH4</t>
+  </si>
+  <si>
+    <t>Mini-split connection</t>
+  </si>
+  <si>
+    <t>MH3</t>
+  </si>
+  <si>
+    <t>Air handler with electric heat, 60A</t>
+  </si>
+  <si>
+    <t>MH13</t>
+  </si>
+  <si>
+    <t>Tankless electric water heater</t>
+  </si>
+  <si>
+    <t>MH14</t>
+  </si>
+  <si>
+    <t>Thermostat low-voltage wiring</t>
+  </si>
+  <si>
+    <t>MH5</t>
+  </si>
+  <si>
+    <t>Rooftop unit (RTU) hookup</t>
+  </si>
+  <si>
+    <t>MH6</t>
+  </si>
+  <si>
+    <t>RTU service receptacle</t>
+  </si>
+  <si>
+    <t>MH9</t>
+  </si>
+  <si>
+    <t>Exhaust fan, commercial</t>
+  </si>
+  <si>
+    <t>MH12</t>
+  </si>
+  <si>
+    <t>Unit heater</t>
+  </si>
+  <si>
+    <t>MH7</t>
+  </si>
+  <si>
+    <t>Walk-in cooler, condensing unit</t>
+  </si>
+  <si>
+    <t>MH8</t>
+  </si>
+  <si>
+    <t>Walk-in cooler, evaporator</t>
+  </si>
+  <si>
+    <t>MH10</t>
+  </si>
+  <si>
+    <t>Motor with starter, 3-phase</t>
+  </si>
+  <si>
+    <t>MH11</t>
+  </si>
+  <si>
+    <t>Motor on VFD</t>
+  </si>
+  <si>
+    <t>LT17</t>
+  </si>
+  <si>
+    <t>Landscape transformer and circuit</t>
+  </si>
+  <si>
+    <t>LT18</t>
+  </si>
+  <si>
+    <t>Landscape light, each</t>
+  </si>
+  <si>
+    <t>LT30</t>
+  </si>
+  <si>
+    <t>Track light, 8 ft with 4 heads</t>
+  </si>
+  <si>
+    <t>DR9</t>
+  </si>
+  <si>
+    <t>4 ft fluorescent to LED, plug-and-play (2-lamp)</t>
+  </si>
+  <si>
+    <t>DR10</t>
+  </si>
+  <si>
+    <t>8 ft fluorescent to LED, single-pin (2-lamp)</t>
+  </si>
+  <si>
+    <t>DR11</t>
+  </si>
+  <si>
+    <t>8 ft HO fluorescent to LED (2-lamp)</t>
+  </si>
+  <si>
+    <t>DR12</t>
+  </si>
+  <si>
+    <t>HID to LED corn lamp</t>
+  </si>
+  <si>
+    <t>DR13</t>
+  </si>
+  <si>
+    <t>Replace HID high bay with LED high bay</t>
+  </si>
+  <si>
+    <t>DR14</t>
+  </si>
+  <si>
+    <t>Replace wall pack</t>
+  </si>
+  <si>
+    <t>DR15</t>
+  </si>
+  <si>
+    <t>Replace exit / emergency light</t>
+  </si>
+  <si>
     <t>STARTER LABOR UNITS — type your own hours, then import.</t>
   </si>
   <si>
@@ -732,10 +1746,13 @@
     <t>8. The import writes hours ONLY — never a price, a name, or a new material.</t>
   </si>
   <si>
-    <t>Assembly hours: the starter assemblies, in a judged most-used-first order (no usage data exists yet). Their hours are the assembly's own typed hours.</t>
-  </si>
-  <si>
-    <t>Keyed by material ID. These IDs are from: mysql://***@127.0.0.1:3307/bidrender_local_b_new, built 2026-10-06T17:59:09.101Z.</t>
+    <t>Assembly hours: ALL 168 starter assemblies (Plan # is the row in references/starter-assemblies-plan.md), in a judged most-used-first order (no usage data exists yet). Their hours are the assembly's own typed hours, and every one is NOT SET until you type it.</t>
+  </si>
+  <si>
+    <t>Grey assembly rows are not in this database yet — the Notes say why (most wait on two database changes: hours that can be 'not set', and two new categories). You can type hours there now to plan; the import skips a row with no ID, so rebuild the sheet once they are seeded and copy your hours across.</t>
+  </si>
+  <si>
+    <t>Keyed by material ID. These IDs are from: mysql://***@127.0.0.1:3307/bidrender_local_b_new, built 2026-10-06T21:32:53.102Z.</t>
   </si>
   <si>
     <t>IDs belong to ONE database. The import checks each row's name against its ID and refuses a mismatch, so a sheet built from another database writes nothing. To import into production, build this sheet from production.</t>
@@ -5114,16 +6131,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>220</v>
       </c>
@@ -5131,109 +6150,2724 @@
         <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="C2" t="s">
+        <v>225</v>
+      </c>
       <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="C3" t="s">
+        <v>228</v>
+      </c>
       <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="C4" t="s">
+        <v>230</v>
+      </c>
       <c r="D4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" t="s">
         <v>226</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="E8" s="2"/>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="B10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="B16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C16" t="s">
+        <v>256</v>
+      </c>
+      <c r="D16" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>229</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" t="s">
-        <v>11</v>
+      <c r="B62" t="s">
+        <v>350</v>
+      </c>
+      <c r="C62" t="s">
+        <v>351</v>
+      </c>
+      <c r="D62" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="3"/>
+      <c r="B112" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="3"/>
+      <c r="B116" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3"/>
+      <c r="B117" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3"/>
+      <c r="B120" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3"/>
+      <c r="B121" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="3"/>
+      <c r="B149" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="3"/>
+      <c r="B150" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="3"/>
+      <c r="B151" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="3"/>
+      <c r="B152" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="3"/>
+      <c r="B155" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="3"/>
+      <c r="B158" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E160" s="3"/>
+      <c r="F160" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="3"/>
+      <c r="B161" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E161" s="3"/>
+      <c r="F161" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="3"/>
+      <c r="B162" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E162" s="3"/>
+      <c r="F162" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E163" s="3"/>
+      <c r="F163" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E167" s="3"/>
+      <c r="F167" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E168" s="3"/>
+      <c r="F168" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E169" s="3"/>
+      <c r="F169" s="3" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5241,7 +8875,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -5249,7 +8883,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>230</v>
+        <v>568</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -5259,42 +8893,42 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>236</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -5304,22 +8938,27 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>239</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>240</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>241</v>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>580</v>
       </c>
     </row>
   </sheetData>
